--- a/category_map.xlsx
+++ b/category_map.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ZENTA</t>
+          <t>BlueRiver Paints</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ZENTA SQB</t>
+          <t>BlueRiver Paints SQB</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ZENTA  TVC</t>
+          <t>BlueRiver Paints TVC</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KALIBU FRESH TVC</t>
+          <t>Nalu Cosmetics TVC</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>KALIBU FRESH SQZBK</t>
+          <t>Nalu Cosmetics SQZBK</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>KALIBU FRESH PROMO</t>
+          <t>Nalu Cosmetics PROMO</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>MOONRIVER BANK</t>
+          <t>Falcon Express Logistics</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -791,7 +791,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MOONRIVER BANK SQZBK</t>
+          <t>Falcon Express Logistics SQZBK</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>MOONRIVER  BANK</t>
+          <t>Falcon Express Logistics</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TUSKAWAVE</t>
+          <t>Lumo Electronics</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AMBER FUELS PROMO</t>
+          <t>PureNectar PROMO</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GOLD LEAF TEA</t>
+          <t>Nile Crest Water</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GOLD LEAF TEA SQ BK</t>
+          <t>Nile Crest Water SQ BK</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BRISK MOTORS</t>
+          <t>Mama's Choice Foods</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1083,7 +1083,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BRISK MOTORS SQB</t>
+          <t>Mama's Choice Foods SQB</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>NALIRI SPA</t>
+          <t>GoldTusk Bank</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>NALIRI SPA SQZBK</t>
+          <t>GoldTusk Bank SQZBK</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>NALIRI SPA CLIP 1</t>
+          <t>GoldTusk Bank CLIP 1</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>PULSE BET TVC</t>
+          <t>Kato's Hardware TVC</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>PULSE BET CLIP 3</t>
+          <t>Kato's Hardware CLIP 3</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RIFT VALLEY OIL</t>
+          <t>Cresta Fuels</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RIFT VALLEY OIL SQ BK</t>
+          <t>Cresta Fuels SQ BK</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>RIFT VA LLEY OIL</t>
+          <t>BrightWave</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CRESTA DAIRY PROMO</t>
+          <t>Amara Skincare PROMO</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SUNBIRD AIRLINES PROMO</t>
+          <t>Kampala Fresh Dairy PROMO</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SUNBIRD AIRLINES SQZBK</t>
+          <t>Kampala Fresh Dairy SQZBK</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SUNBIRD AIRLINES SQZBK</t>
+          <t>Kampala Fresh Dairy SQZBK</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1635,7 +1635,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>SUNBIRD AIRLINES CLIP 1</t>
+          <t>Kampala Fresh Dairy CLIP 1</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MASINDI RESORT TVC</t>
+          <t>EmeraldTel TVC</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>MASINDI RESORT SQB</t>
+          <t>EmeraldTel SQB</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>KAWEESA HARDWARE</t>
+          <t>ZenGlow</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>KAWEESA HARDWARE SQB</t>
+          <t>ZenGlow SQB</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>KAWEESA HARDWARE  SQZBK</t>
+          <t>ZenGlow SQZBK</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1875,7 +1875,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>BLUE HORIZON PAINT TVC</t>
+          <t>Kiboko Insurance TVC</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>BLUE HORIZON PAINT SQB</t>
+          <t>Kiboko Insurance SQB</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>VELVET SOAP</t>
+          <t>Rolex Express</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TROPIC FIZZ PROMO</t>
+          <t>Zawadi Fashion PROMO</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>IRON GATE CEMENT</t>
+          <t>TeraLink</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRON GATE CEMENT </t>
+          <t>TeraLink</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>IRON GATE CEMENT CLIP 2</t>
+          <t>TeraLink CLIP 2</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SAVANNA TELECOM PROMO</t>
+          <t>Ridgeway Furniture PROMO</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>SAVANNA TELECOM SQZBK</t>
+          <t>Ridgeway Furniture SQZBK</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SAVANNA TELEC0M</t>
+          <t>Ridgeway Furniture</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>NILEBORN WATER TVC</t>
+          <t>SunCrest Bakery TVC</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>NILEBORN WATER SQ BK</t>
+          <t>SunCrest Bakery SQ BK</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>COPPER HILL MINING</t>
+          <t>Savanna Sip</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>COPPER HILL MINING SQ BK</t>
+          <t>Savanna Sip SQ BK</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2443,7 +2443,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>COPPER  HILL MINING TVC</t>
+          <t>Savanna Sip TVC</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>EQUATOR FM</t>
+          <t>Nyati Motors</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2527,7 +2527,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>EQUATOR FM SQ BK</t>
+          <t>Nyati Motors SQ BK</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>BUGOLOBI ESTATES</t>
+          <t>Cedar Grove Realty</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>BUGOLOBI ESTATES SQZBK</t>
+          <t>Cedar Grove Realty SQZBK</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2655,7 +2655,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>BUG0LOBI ESTATES PROMO</t>
+          <t>Cedar Grove Realty PROMO</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>KATO'S GRILL PROMO</t>
+          <t>Highland Brew PROMO</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>PEARL LINE FERRIES</t>
+          <t>Pemba Tyres</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>MAGIC LOAF BAKERY TVC</t>
+          <t>CrestLine Foods TVC</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RUBY CROWN HOTEL</t>
+          <t>Twiga Airtime</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>STARLIGHT CINEMA TVC</t>
+          <t>BlueRiver Paints TVC</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2899,7 +2899,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>STARLIGHT CINEMA SQZBK</t>
+          <t>BlueRiver Paints SQZBK</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Starlight Cinema PROMO</t>
+          <t>BlueRiver Paints PROMO</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ZAWADI JEWELS TVC</t>
+          <t>Nalu Cosmetics TVC</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ZAWADI JEWELS SQB</t>
+          <t>Nalu Cosmetics SQB</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>FALCON COURIERS PROMO</t>
+          <t>Falcon Express Logistics PROMO</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>FALCON COURIERS SQZBK</t>
+          <t>Falcon Express Logistics SQZBK</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GREENFIELD SACCO PROMO</t>
+          <t>Lumo Electronics PROMO</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GREENFIELD SACCO SQZBK</t>
+          <t>Lumo Electronics SQZBK</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3231,7 +3231,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>AMANI INSURANCE TVC</t>
+          <t>PureNectar TVC</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>AMANI INSURANCE SQB</t>
+          <t>PureNectar SQB</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>TWILIGHT BREWERY</t>
+          <t>Nile Crest Water</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3359,7 +3359,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Twilight Brewery SQB</t>
+          <t>Nile Crest Water SQB</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3399,7 +3399,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>KISORO COFFEE PROMO</t>
+          <t>Mama's Choice Foods PROMO</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3439,7 +3439,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KISORO COFFEE SQB</t>
+          <t>Mama's Choice Foods SQB</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>NORTHWIND CARGO PROMO</t>
+          <t>GoldTusk Bank PROMO</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>LAKEVIEW CLINIC TVC</t>
+          <t>Kato's Hardware TVC</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>LAKEVIEW CLINIC SQ BK</t>
+          <t>Kato's Hardware SQ BK</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3607,7 +3607,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Lakeview Clinic</t>
+          <t>Kato's Hardware</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3647,7 +3647,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>COBALT ELECTRONICS</t>
+          <t>Cresta Fuels</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>COBALT ELECTRONICS SQZBK</t>
+          <t>Cresta Fuels SQZBK</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Cobalt Electronics SQ BK</t>
+          <t>Cresta Fuels SQ BK</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>RAINBOW DAYCARE TVC</t>
+          <t>BrightWave TVC</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>RAINBOW DAYCARE SQB</t>
+          <t>BrightWave SQB</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Rainbow Daycare</t>
+          <t>BrightWave</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>MPIGI TIMBER</t>
+          <t>Amara Skincare</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -3947,7 +3947,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>MPIGI TIMBER SQ BK</t>
+          <t>Amara Skincare SQ BK</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Mpigi Timber PROMO</t>
+          <t>Amara Skincare PROMO</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>HORIZON UNIVERSITY TVC</t>
+          <t>Kampala Fresh Dairy TVC</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>HORIZON UNIVERSITY SQ BK</t>
+          <t>Kampala Fresh Dairy SQ BK</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>H0RIZON UNIVERSITY SQZBK</t>
+          <t>Kampala Fresh Dairy SQZBK</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>SUNCITY MALL PROMO</t>
+          <t>EmeraldTel PROMO</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>SUNCITY MALL PROMO</t>
+          <t>EmeraldTel PROMO</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>EBONY FASHION</t>
+          <t>ZenGlow</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>EBONY FASHION SQZBK</t>
+          <t>ZenGlow SQZBK</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4315,7 +4315,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>TRIBE RADIO PROMO</t>
+          <t>Kiboko Insurance PROMO</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4355,7 +4355,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>TRIBE RADIO CLIP 3</t>
+          <t>Kiboko Insurance CLIP 3</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>KAJANSI GARDENS</t>
+          <t>Rolex Express</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>CASCADE WATER PROMO</t>
+          <t>Zawadi Fashion PROMO</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>CASCADE WATER SQZBK</t>
+          <t>Zawadi Fashion SQZBK</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>CASCADE  WATER TVC</t>
+          <t>Zawadi Fashion TVC</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>MARBLE ARCH REALTY PROMO</t>
+          <t>TeraLink PROMO</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4599,7 +4599,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>MARBLE ARCH REALTY SQZBK</t>
+          <t>TeraLink SQZBK</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -4643,7 +4643,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GOLDCREST SEEDS</t>
+          <t>Ridgeway Furniture</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GOLDCREST SEEDS SQZBK</t>
+          <t>Ridgeway Furniture SQZBK</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>PALM ROYAL SOAP TVC</t>
+          <t>SunCrest Bakery TVC</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>PALM ROYAL SOAP SQB</t>
+          <t>SunCrest Bakery SQB</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>JINJA RIVER TOURS PROMO</t>
+          <t>Savanna Sip PROMO</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -4847,7 +4847,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>JINJA RIVER TOURS SQ BK</t>
+          <t>Savanna Sip SQ BK</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>JINJA RIVER T0URS SQZBK</t>
+          <t>Savanna Sip SQZBK</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>VICTORY GYM TVC</t>
+          <t>Nyati Motors TVC</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>VICTORY GYM SQZBK</t>
+          <t>Nyati Motors SQZBK</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>CHERRY BLOSSOM SALON</t>
+          <t>Cedar Grove Realty</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5047,7 +5047,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>CHERRY BLOSSOM SALON SQZBK</t>
+          <t>Cedar Grove Realty SQZBK</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>IRONWOOD FURNITURE PROMO</t>
+          <t>Highland Brew PROMO</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>IRONWOOD FURNITURE  SQB</t>
+          <t>Highland Brew SQB</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>(SPOTLIGHT PROMO)</t>
+          <t>(Pemba Tyres PROMO)</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5219,7 +5219,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>MASAKA TOUR SQZBK</t>
+          <t>CrestLine Foods SQZBK</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5263,7 +5263,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>RIVERBANK MENTION</t>
+          <t>Twiga Airtime MENTION</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5307,7 +5307,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GOLDCREST SQB</t>
+          <t>BlueRiver Paints SQB</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>TRIBE RADIO SQ BK</t>
+          <t>Kiboko Insurance SQ BK</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5395,7 +5395,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>COBALT TVC TVC</t>
+          <t>Nalu Cosmetics TVC</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5439,7 +5439,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>IRONWOOD SQ  BK</t>
+          <t>Falcon Express Logistics SQ  BK</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">

--- a/category_map.xlsx
+++ b/category_map.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Diaspora</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Diaspora</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Diaspora</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Diaspora</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Diaspora</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Diaspora</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Diaspora</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Diaspora</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Diaspora</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Diaspora</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Retail Partner</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Trade Marketing</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Diaspora</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Diaspora</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Youth Segment</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Civic Notice</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Diaspora</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Broadcast Original</t>
+          <t>Swap</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Diaspora</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
